--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>SKU</t>
   </si>
@@ -36,9 +35,6 @@
     <t>产品名称</t>
   </si>
   <si>
-    <t>实体仓名称</t>
-  </si>
-  <si>
     <t>实体仓可用库存</t>
   </si>
   <si>
@@ -48,7 +44,16 @@
     <t>实体仓未分配数</t>
   </si>
   <si>
-    <t>虚拟仓库存数</t>
+    <t>虚拟仓</t>
+  </si>
+  <si>
+    <t>虚拟仓库存</t>
+  </si>
+  <si>
+    <t>虚拟仓可用库存</t>
+  </si>
+  <si>
+    <t>虚拟仓冻结库存</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -60,16 +65,22 @@
     <t>{.warehouseName}</t>
   </si>
   <si>
-    <t>{.usableQty}</t>
-  </si>
-  <si>
     <t>{.distributionQty}</t>
   </si>
   <si>
     <t>{.unDistributionQty}</t>
   </si>
   <si>
+    <t>{.virtualWarehouseName}</t>
+  </si>
+  <si>
     <t>{.virtualQty}</t>
+  </si>
+  <si>
+    <t>{.virtualUsableQty}</t>
+  </si>
+  <si>
+    <t>{.virtualFrozenQty}</t>
   </si>
 </sst>
 </file>
@@ -242,12 +253,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -583,7 +600,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -607,16 +624,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -625,97 +642,100 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1028,19 +1048,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.25" customWidth="1"/>
     <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="25.125" customWidth="1"/>
+    <col min="3" max="3" width="21.875" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="16.25" customWidth="1"/>
-    <col min="6" max="6" width="16.5" customWidth="1"/>
-    <col min="7" max="7" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="23" customWidth="1"/>
+    <col min="7" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="16.5" customWidth="1"/>
+    <col min="9" max="9" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,34 +1078,46 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1091,15 +1125,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -62,7 +62,7 @@
     <t>{.productName}</t>
   </si>
   <si>
-    <t>{.warehouseName}</t>
+    <t>{.usableQty}</t>
   </si>
   <si>
     <t>{.distributionQty}</t>

--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="虚拟仓差异" sheetId="1" r:id="rId1"/>
+    <sheet name="实体仓库分配统计" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
   <si>
     <t>SKU</t>
   </si>
@@ -81,6 +82,18 @@
   </si>
   <si>
     <t>{.virtualFrozenQty}</t>
+  </si>
+  <si>
+    <t>实体仓编号</t>
+  </si>
+  <si>
+    <t>实体仓名称</t>
+  </si>
+  <si>
+    <t>{.warehouseCode}</t>
+  </si>
+  <si>
+    <t>{.warehouseName}</t>
   </si>
 </sst>
 </file>
@@ -1125,4 +1138,71 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="1" width="13.75" customWidth="1"/>
+    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="3" max="3" width="17.375" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="16.5" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="20.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="1"/>
+    <workbookView windowWidth="24045" windowHeight="12375"/>
   </bookViews>
   <sheets>
-    <sheet name="虚拟仓差异" sheetId="1" r:id="rId1"/>
-    <sheet name="实体仓库分配统计" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>SKU</t>
   </si>
@@ -82,18 +81,6 @@
   </si>
   <si>
     <t>{.virtualFrozenQty}</t>
-  </si>
-  <si>
-    <t>实体仓编号</t>
-  </si>
-  <si>
-    <t>实体仓名称</t>
-  </si>
-  <si>
-    <t>{.warehouseCode}</t>
-  </si>
-  <si>
-    <t>{.warehouseName}</t>
   </si>
 </sst>
 </file>
@@ -1138,71 +1125,4 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
-  <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="2" width="14.75" customWidth="1"/>
-    <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="20.25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>SKU</t>
   </si>
@@ -36,6 +36,12 @@
     <t>产品名称</t>
   </si>
   <si>
+    <t>实体仓实际库存</t>
+  </si>
+  <si>
+    <t>实体仓冻结库存</t>
+  </si>
+  <si>
     <t>实体仓可用库存</t>
   </si>
   <si>
@@ -61,6 +67,12 @@
   </si>
   <si>
     <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.realQty}</t>
+  </si>
+  <si>
+    <t>{.frozenQty}</t>
   </si>
   <si>
     <t>{.usableQty}</t>
@@ -1061,40 +1073,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="10.25" customWidth="1"/>
     <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="21.875" customWidth="1"/>
-    <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="23" customWidth="1"/>
-    <col min="7" max="7" width="14.625" customWidth="1"/>
-    <col min="8" max="8" width="16.5" customWidth="1"/>
-    <col min="9" max="9" width="15.875" customWidth="1"/>
+    <col min="3" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="15.5" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="9" max="9" width="14.625" customWidth="1"/>
+    <col min="10" max="10" width="16.5" customWidth="1"/>
+    <col min="11" max="11" width="15.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="3" t="s">
@@ -1103,34 +1116,46 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1163,42 +1188,42 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>SKU</t>
   </si>
@@ -1168,19 +1168,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="6"/>
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="13.75" customWidth="1"/>
     <col min="2" max="2" width="14.75" customWidth="1"/>
     <col min="3" max="3" width="17.375" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16.5" customWidth="1"/>
-    <col min="6" max="6" width="17" customWidth="1"/>
-    <col min="7" max="7" width="20.25" customWidth="1"/>
+    <col min="4" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="21.875" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="20.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:7">
+    <row r="1" s="1" customFormat="1" ht="14.25" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1194,16 +1195,22 @@
         <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1217,12 +1224,18 @@
         <v>25</v>
       </c>
       <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
     </row>

--- a/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/virtualInventoryDiff.xlsx
@@ -1198,7 +1198,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -1227,7 +1227,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
         <v>15</v>
